--- a/config/data/Selector.xlsx
+++ b/config/data/Selector.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Selector" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Selector" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1451,7 +1451,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1461,7 +1461,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>Fault</t>
+          <t>NoOp</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
